--- a/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_1_biases.xlsx
+++ b/Unit 6. Neural Models, Vision, and Foundation Models/6.1 Multi-layer Perceptron (MLP)/weights_and_biases/layer_1_biases.xlsx
@@ -457,7 +457,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.02936278575380626</v>
+        <v>-0.02936278575380625</v>
       </c>
     </row>
     <row r="7">
@@ -467,7 +467,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.3908475314211368</v>
+        <v>0.3908475314211369</v>
       </c>
     </row>
     <row r="9">
@@ -492,7 +492,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.124831153548595</v>
+        <v>-0.1248311535485951</v>
       </c>
     </row>
     <row r="14">
@@ -502,7 +502,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.002538992939853483</v>
+        <v>0.002538992939853482</v>
       </c>
     </row>
     <row r="16">
@@ -527,7 +527,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.09016502958109299</v>
+        <v>-0.090165029581093</v>
       </c>
     </row>
     <row r="21">
